--- a/stories/arbres/ATOM-EMO.LEX.004-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nassim est dans la cuisine avec papa. Papa soulève le couvercle. Un petit nuage de vapeur sort. Nassim sent son cœur battre vite. Ses yeux s'ouvrent. Nassim dit : je suis surpris. Être surpris, ce n'est pas honteux. Papa dit : d'abord respirer. Ensuite comprendre, avant d'agir. Nassim souffle une grande fois. Il regarde la casserole. Il dit : je veux comprendre. C'est la vapeur. Rien n'est cassé. Plus tard, ils vont au jardin. Un oiseau s'envole près de Nassim. Nassim sent encore le cœur. Il dit : je suis surpris. Il souffle. Il veut respirer. Il regarde. C'est un merle. Nassim comprend. Il sourit. Dans la cuisine, puis au jardin, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
+          <t>Nassim est dans la cuisine avec papa. Papa soulève le couvercle. Un petit nuage de vapeur sort. Nassim sent son cœur battre vite. Ses yeux s'ouvrent. Je suis surpris. Être surpris, ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Nassim souffle une grande fois. Il regarde la casserole. Je veux comprendre. C'est la vapeur. Rien n'est cassé. Plus tard, ils vont au jardin. Un oiseau s'envole près de Nassim. Nassim sent encore le cœur. Je suis surpris. Il souffle. Il veut respirer. Il regarde. C'est un merle. Nassim comprend. Il sourit. Dans la cuisine, puis au jardin, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nassim est dans la cuisine avec papa. Papa soulève le couvercle. Un petit nuage de vapeur sort. Nassim sent son cœur battre vite. Ses yeux s'ouvrent.
+enfant-m|Je suis surpris. Être surpris, ce n'est pas honteux.
+papa|D'abord respirer. Ensuite comprendre, avant d'agir.
+narrateur|Nassim souffle une grande fois. Il regarde la casserole.
+narrateur|Je veux comprendre. C'est la vapeur. Rien n'est cassé. Plus tard, ils vont au jardin.
+narrateur|Un oiseau s'envole près de Nassim. Nassim sent encore le cœur.
+narrateur|Je suis surpris. Il souffle. Il veut respirer.
+narrateur|Il regarde. C'est un merle. Nassim comprend. Il sourit. Dans la cuisine, puis au jardin, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Nassim est surpris. Que fait-il d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nassim a nommé : surpris. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nassim et papa restent au jardin. Le merle chante.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Il regarde. C'est un merle. Nassim comprend. Il sourit. Dans la cuisine, puis au jardin, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Nassim est surpris. Que fait-il d'abord ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Nassim a nommé : surpris. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Nassim et papa restent au jardin. Le merle chante.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.004-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nassim est surpris deux fois</t>
+          <t>Raphaël, la vapeur et le merle</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël est surpris par la vapeur, puis par un merle. Il nomme, il souffle, il comprend.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nassim est dans la cuisine avec papa. Papa soulève le couvercle. Un petit nuage de vapeur sort. Nassim sent son cœur battre vite. Ses yeux s'ouvrent. Je suis surpris. Être surpris, ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Nassim souffle une grande fois. Il regarde la casserole. Je veux comprendre. C'est la vapeur. Rien n'est cassé. Plus tard, ils vont au jardin. Un oiseau s'envole près de Nassim. Nassim sent encore le cœur. Je suis surpris. Il souffle. Il veut respirer. Il regarde. C'est un merle. Nassim comprend. Il sourit. Dans la cuisine, puis au jardin, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
+          <t>La vitre de la cuisine est embuée. Une goutte glisse tout doucement. La maison sent la soupe aux carottes. La casserole chante tout bas. Papa essuie la table en bois. Maman coupe le pain. Le pain est encore un peu chaud. Une miette tombe près de l'assiette. Dehors, une gouttière goutte. Raphaël, tu sens la soupe ? Oui. Ça sent bon. Le couvercle tremble un peu. En ce moment, papa soulève le couvercle. Un petit nuage de vapeur sort. Le nuage est blanc et tiède. Raphaël sent son cœur battre vite. Ses yeux s'ouvrent tout grands. Je suis surpris. Être surpris, ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Raphaël souffle une grande fois. Il souffle encore. Tu as soufflé. Bravo. Qu'est-ce que tu vois ? Je veux comprendre. Raphaël regarde la casserole. Il reste un peu loin. C'est la vapeur. Oui. C'est la soupe. Rien n'est cassé. Le cœur de Raphaël se calme. Plus tard, ils vont au jardin. L'herbe est encore un peu mouillée. Un seau bleu attend près du bac. Un merle picore tout près. L'oiseau s'envole d'un coup. Voup. Raphaël sent encore son cœur. Je suis surpris. D'abord respirer. Raphaël souffle. Il souffle encore une fois. Tu as soufflé. Qu'est-ce que tu vois ? Raphaël regarde. C'est un merle. Oui. Il picore. Je comprends. On nomme : surpris. On respire. On cherche à comprendre. Raphaël sourit. Le merle chante dans le pommier. Tu as soufflé deux fois. Tu as compris deux fois. Surpris. Puis calme. L'herbe colle un peu aux chaussettes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nassim est dans la cuisine avec papa. Papa soulève le couvercle. Un petit nuage de vapeur sort. Nassim sent son cœur battre vite. Ses yeux s'ouvrent.
-enfant-m|Je suis surpris. Être surpris, ce n'est pas honteux.
-papa|D'abord respirer. Ensuite comprendre, avant d'agir.
-narrateur|Nassim souffle une grande fois. Il regarde la casserole.
-narrateur|Je veux comprendre. C'est la vapeur. Rien n'est cassé. Plus tard, ils vont au jardin.
-narrateur|Un oiseau s'envole près de Nassim. Nassim sent encore le cœur.
-narrateur|Je suis surpris. Il souffle. Il veut respirer.
-narrateur|Il regarde. C'est un merle. Nassim comprend. Il sourit. Dans la cuisine, puis au jardin, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La vitre de la cuisine est embuée.
+narrateur|Une goutte glisse tout doucement.
+narrateur|La maison sent la soupe aux carottes.
+narrateur|La casserole chante tout bas.
+narrateur|Papa essuie la table en bois.
+narrateur|Maman coupe le pain.
+narrateur|Le pain est encore un peu chaud.
+narrateur|Une miette tombe près de l'assiette.
+narrateur|Dehors, une gouttière goutte.
+maman|Raphaël, tu sens la soupe ?
+enfant-m|Oui. Ça sent bon.
+papa|Le couvercle tremble un peu.
+narrateur|En ce moment, papa soulève le couvercle.
+narrateur|Un petit nuage de vapeur sort.
+narrateur|Le nuage est blanc et tiède.
+narrateur|Raphaël sent son cœur battre vite.
+narrateur|Ses yeux s'ouvrent tout grands.
+enfant-m|Je suis surpris.
+maman|Être surpris, ce n'est pas honteux.
+papa|D'abord respirer.
+papa|Ensuite comprendre, avant d'agir.
+narrateur|Raphaël souffle une grande fois.
+narrateur|Il souffle encore.
+papa|Tu as soufflé. Bravo.
+papa|Qu'est-ce que tu vois ?
+enfant-m|Je veux comprendre.
+narrateur|Raphaël regarde la casserole.
+narrateur|Il reste un peu loin.
+enfant-m|C'est la vapeur.
+maman|Oui. C'est la soupe.
+papa|Rien n'est cassé.
+narrateur|Le cœur de Raphaël se calme.
+narrateur|Plus tard, ils vont au jardin.
+narrateur|L'herbe est encore un peu mouillée.
+narrateur|Un seau bleu attend près du bac.
+narrateur|Un merle picore tout près.
+narrateur|L'oiseau s'envole d'un coup.
+narrateur|Voup.
+narrateur|Raphaël sent encore son cœur.
+enfant-m|Je suis surpris.
+papa|D'abord respirer.
+narrateur|Raphaël souffle.
+narrateur|Il souffle encore une fois.
+maman|Tu as soufflé. Qu'est-ce que tu vois ?
+narrateur|Raphaël regarde.
+enfant-m|C'est un merle.
+papa|Oui. Il picore.
+enfant-m|Je comprends.
+maman|On nomme : surpris.
+papa|On respire. On cherche à comprendre.
+narrateur|Raphaël sourit.
+narrateur|Le merle chante dans le pommier.
+papa|Tu as soufflé deux fois.
+maman|Tu as compris deux fois.
+enfant-m|Surpris. Puis calme.
+narrateur|L'herbe colle un peu aux chaussettes.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cuisine,oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nassim est surpris. Que fait-il d'abord ?</t>
+          <t>Raphaël est surpris. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nassim est surpris. Que fait-il d'abord ?</t>
+          <t>narrateur|Raphaël est surpris.
+narrateur|Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nassim a nommé : surpris. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir.</t>
+          <t>Raphaël a nommé : surpris. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir. Tu as respiré. Bravo. Tu as regardé. Tu as compris. C'était la vapeur. Puis le merle. Rien n'était cassé. Être surpris, ce n'est pas honteux. Raphaël pose la main sur son ventre. Son ventre est plus calme. Je souffle encore un peu. Oui. On respire. On cherche à comprendre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,10 +1744,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nassim a nommé : surpris. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël a nommé : surpris.
+narrateur|Deux fois.
+narrateur|Il a soufflé.
+narrateur|Il a voulu comprendre avant d'agir.
+papa|Tu as respiré. Bravo.
+maman|Tu as regardé. Tu as compris.
+enfant-m|C'était la vapeur. Puis le merle.
+papa|Rien n'était cassé.
+maman|Être surpris, ce n'est pas honteux.
+narrateur|Raphaël pose la main sur son ventre.
+narrateur|Son ventre est plus calme.
+enfant-m|Je souffle encore un peu.
+papa|Oui. On respire. On cherche à comprendre.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nassim et papa restent au jardin. Le merle chante.</t>
+          <t>Raphaël et papa restent au jardin. Le merle chante. L'herbe brille un peu. On laisse le seau près du bac ? Oui. Le merle picore encore. Tu as nommé. Tu as soufflé. Je suis calme, maintenant. La soupe attend à la cuisine. On rentre tout doux. Les chaussures sont un peu mouillées. Le pommier bouge.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,10 +1924,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nassim et papa restent au jardin. Le merle chante.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Raphaël et papa restent au jardin.
+narrateur|Le merle chante.
+narrateur|L'herbe brille un peu.
+maman|On laisse le seau près du bac ?
+enfant-m|Oui. Le merle picore encore.
+papa|Tu as nommé. Tu as soufflé.
+enfant-m|Je suis calme, maintenant.
+maman|La soupe attend à la cuisine.
+papa|On rentre tout doux.
+narrateur|Les chaussures sont un peu mouillées.
+narrateur|Le pommier bouge.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1871,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais surpris. J'ai soufflé. Tu as compris. Bravo. Le merle a chanté. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2106,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais surpris. J'ai soufflé.
+papa|Tu as compris. Bravo.
+maman|Le merle a chanté.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2169,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-04.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nassim est dans la cuisine avec papa. Papa soulève le couvercle. Un petit nuage de vapeur sort. Nassim sent son cœur battre vite. Ses yeux s'ouvrent. Nassim dit : je suis &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;. Être surpris, ce n'est pas honteux. Papa dit : d'abord respirer. Ensuite comprendre, avant d'agir. Nassim souffle une grande fois. Il regarde la casserole. Il dit : je veux comprendre. C'est la vapeur. Rien n'est cassé. Plus tard, ils vont au jardin. Un oiseau s'envole près de Nassim. Nassim sent encore le cœur. Il dit : je suis surpris. Il souffle. Il veut respirer. Il regarde. C'est un merle. Nassim comprend. Il sourit. Dans la cuisine, puis au jardin, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre de la cuisine est embuée. Une goutte glisse tout doucement. La maison sent la soupe aux carottes. La casserole chante tout bas. Papa essuie la table en bois. Maman coupe le pain. Le pain est encore un peu chaud. Une miette tombe près de l'assiette. Dehors, une gouttière goutte. Raphaël, tu sens la soupe ? Oui. Ça sent bon. Le couvercle tremble un peu. En ce moment, papa soulève le couvercle. Un petit nuage de vapeur sort. Le nuage est blanc et tiède. Raphaël sent son cœur battre vite. Ses yeux s'ouvrent tout grands. Je suis surpris. Être surpris, ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Raphaël souffle une grande fois. Il souffle encore. Tu as soufflé. Bravo. Qu'est-ce que tu vois ? Je veux comprendre. Raphaël regarde la casserole. Il reste un peu loin. C'est la vapeur. Oui. C'est la soupe. Rien n'est cassé. Le cœur de Raphaël se calme. Plus tard, ils vont au jardin. L'herbe est encore un peu mouillée. Un seau bleu attend près du bac. Un merle picore tout près. L'oiseau s'envole d'un coup. Voup. Raphaël sent encore son cœur. Je suis surpris. D'abord respirer. Raphaël souffle. Il souffle encore une fois. Tu as soufflé. Qu'est-ce que tu vois ? Raphaël regarde. C'est un merle. Oui. Il picore. Je comprends. On nomme : surpris. On respire. On cherche à comprendre. Raphaël sourit. Le merle chante dans le pommier. Tu as soufflé deux fois. Tu as compris deux fois. Surpris. Puis calme. L'herbe colle un peu aux chaussettes.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nassim est &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;. Que fait-il d'abord ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël est surpris. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1575,6 @@
 narrateur|Que fait-il d'abord ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1605,7 +1604,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nassim a nommé : &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a nommé : surpris. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir. Tu as respiré. Bravo. Tu as regardé. Tu as compris. C'était la vapeur. Puis le merle. Rien n'était cassé. Être surpris, ce n'est pas honteux. Raphaël pose la main sur son ventre. Son ventre est plus calme. Je souffle encore un peu. Oui. On respire. On cherche à comprendre.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1793,7 +1792,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nassim et papa restent au jardin. Le merle chante.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël et papa restent au jardin. Le merle chante. L'herbe brille un peu. On laisse le seau près du bac ? Oui. Le merle picore encore. Tu as nommé. Tu as soufflé. Je suis calme, maintenant. La soupe attend à la cuisine. On rentre tout doux. Les chaussures sont un peu mouillées. Le pommier bouge.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1966,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais surpris. J'ai soufflé. Tu as compris. Bravo. Le merle a chanté. L'histoire est finie.</t>
+          <t>J'étais surpris. J'ai soufflé. Tu as compris. Bravo. Le merle a chanté.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais surpris. J'ai soufflé. Tu as compris. Bravo. Le merle a chanté.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,11 +2107,9 @@
         <is>
           <t>enfant-m|J'étais surpris. J'ai soufflé.
 papa|Tu as compris. Bravo.
-maman|Le merle a chanté.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Le merle a chanté.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2131,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2176,6 +2173,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nassim, papa</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
